--- a/hall/resources/sample/PopularityRanking.xlsx
+++ b/hall/resources/sample/PopularityRanking.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -128,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>序列ID</t>
   </si>
@@ -181,52 +186,61 @@
     <t>2</t>
   </si>
   <si>
-    <t>1990000_4000000</t>
-  </si>
-  <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
+    <t>1990000_4000000|1024007_100</t>
+  </si>
+  <si>
+    <t>1990000_3000000|1024007_90</t>
+  </si>
+  <si>
+    <t>1990000_2000000|1024007_80</t>
+  </si>
+  <si>
+    <t>1990000_1000000|1024007_70</t>
+  </si>
+  <si>
+    <t>1990000_500000|1024007_60</t>
   </si>
   <si>
     <t>11_15</t>
   </si>
   <si>
-    <t>1990000_200000</t>
+    <t>1990000_200000|1024007_50</t>
   </si>
   <si>
     <t>16_20</t>
   </si>
   <si>
-    <t>1990000_100000</t>
+    <t>1990000_100000|1024007_40</t>
   </si>
   <si>
     <t>21_25</t>
   </si>
   <si>
+    <t>1990000_100000|1024007_35</t>
+  </si>
+  <si>
     <t>26_30</t>
   </si>
   <si>
+    <t>1990000_100000|1024007_30</t>
+  </si>
+  <si>
     <t>31_40</t>
   </si>
   <si>
-    <t>1990000_50000</t>
+    <t>1990000_50000|1024007_25</t>
   </si>
   <si>
     <t>41_50</t>
   </si>
   <si>
+    <t>1990000_50000|1024007_20</t>
+  </si>
+  <si>
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1990000_20000|1024007_10</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1453,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="31.25" customWidth="1"/>
     <col min="6" max="6" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1741,7 +1755,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -1753,13 +1767,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -1771,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F19" s="9"/>
     </row>
@@ -1789,13 +1803,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -1807,13 +1821,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F21" s="9"/>
     </row>

--- a/hall/resources/sample/PopularityRanking.xlsx
+++ b/hall/resources/sample/PopularityRanking.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>序列ID</t>
   </si>
@@ -186,61 +186,73 @@
     <t>2</t>
   </si>
   <si>
-    <t>1990000_4000000|1024007_100</t>
-  </si>
-  <si>
-    <t>1990000_3000000|1024007_90</t>
-  </si>
-  <si>
-    <t>1990000_2000000|1024007_80</t>
-  </si>
-  <si>
-    <t>1990000_1000000|1024007_70</t>
-  </si>
-  <si>
-    <t>1990000_500000|1024007_60</t>
+    <t>1990000_4000000|1024007_100|1980000_500</t>
+  </si>
+  <si>
+    <t>1990000_3000000|1024007_90|1980000_480</t>
+  </si>
+  <si>
+    <t>1990000_2000000|1024007_80|1980000_450</t>
+  </si>
+  <si>
+    <t>1990000_1000000|1024007_70|1980000_420</t>
+  </si>
+  <si>
+    <t>1990000_500000|1024007_60|1980000_360</t>
+  </si>
+  <si>
+    <t>1990000_500000|1024007_60|1980000_350</t>
+  </si>
+  <si>
+    <t>1990000_500000|1024007_60|1980000_320</t>
+  </si>
+  <si>
+    <t>1990000_500000|1024007_60|1980000_300</t>
+  </si>
+  <si>
+    <t>1990000_500000|1024007_60|1980000_280</t>
   </si>
   <si>
     <t>11_15</t>
   </si>
   <si>
-    <t>1990000_200000|1024007_50</t>
+    <t>1990000_200000|1024007_50|1980000_260</t>
   </si>
   <si>
     <t>16_20</t>
   </si>
   <si>
-    <t>1990000_100000|1024007_40</t>
+    <t>1990000_100000|1024007_40|1980000_240</t>
   </si>
   <si>
     <t>21_25</t>
   </si>
   <si>
-    <t>1990000_100000|1024007_35</t>
+    <t>1990000_100000|1024007_35|1980000_220</t>
   </si>
   <si>
     <t>26_30</t>
   </si>
   <si>
-    <t>1990000_100000|1024007_30</t>
+    <t>1990000_100000|1024007_30|1980000_200</t>
   </si>
   <si>
     <t>31_40</t>
   </si>
   <si>
-    <t>1990000_50000|1024007_25</t>
+    <t>1990000_50000|1024007_25|1980000_180</t>
   </si>
   <si>
     <t>41_50</t>
   </si>
   <si>
-    <t>1990000_50000|1024007_20</t>
+    <t>1990000_50000|1024007_20|1980000_150</t>
   </si>
   <si>
     <t>51_100</t>
   </si>
   <si>
-    <t>1990000_20000|1024007_10</t>
+    <t>1990000_20000|1024007_10|1980000_100</t>
   </si>
 </sst>
 </file>
@@ -1647,7 +1659,7 @@
         <v>16</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="9"/>
     </row>
@@ -1665,7 +1677,7 @@
         <v>16</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -1683,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F13" s="9"/>
     </row>
@@ -1701,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -1713,13 +1725,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -1731,13 +1743,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -1749,13 +1761,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -1767,13 +1779,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -1785,13 +1797,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F19" s="9"/>
     </row>
@@ -1803,13 +1815,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -1821,13 +1833,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F21" s="9"/>
     </row>
